--- a/质检报告/数据处理报告.xlsx
+++ b/质检报告/数据处理报告.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_摸底检查" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_质检问题" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_入库记录" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_数据统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="00_总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_摸底检查" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_质检问题" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_入库记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_数据统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -464,7 +452,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -524,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-18 19:59:51</t>
+          <t>2026-05-24 21:38:15</t>
         </is>
       </c>
     </row>
@@ -543,37 +531,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>文件名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>要素/像素</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>坐标系</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>几何类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>值域范围</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -582,17 +570,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corrupt_crs.shp</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>corrupt_crs.geojson</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>矢量</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EPSG:4214</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>['Point']</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>读取失败: 'utf-8' codec can't decode byte 0xe4 in position 9: unexpected end of data</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -769,7 +771,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GEOGCS["WGS 84",DATUM["WGS_1984",SPHEROID["WGS 84"</t>
+          <t>EPSG:4326</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -795,31 +797,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E466"/>
+  <dimension ref="A1:E469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>规则</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>规则名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>问题说明</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>详细信息</t>
         </is>
@@ -874,29 +876,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corrupt_geometry.geojson</t>
+          <t>shanghai_buildings.geojson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>面重叠检查</t>
+          <t>NULL比例</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>发现1对面重叠</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[{'要素A': '3', '要素B': '5', '重叠面积': 0.00059246}]</t>
-        </is>
-      </c>
+          <t>字段"name"NULL值占比92.9%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,7 +914,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>字段"name"NULL值占比92.9%</t>
+          <t>字段"name:zh"NULL值占比99.0%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -939,7 +937,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>字段"name:zh"NULL值占比99.0%</t>
+          <t>字段"name:zh-Hans"NULL值占比99.5%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -962,7 +960,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>字段"name:zh-Hans"NULL值占比99.5%</t>
+          <t>字段"name:zh-Hant"NULL值占比99.5%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -985,7 +983,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>字段"name:zh-Hant"NULL值占比99.5%</t>
+          <t>字段"note"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1008,7 +1006,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>字段"note"NULL值占比99.9%</t>
+          <t>字段"amenity"NULL值占比99.0%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1031,7 +1029,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>字段"amenity"NULL值占比99.0%</t>
+          <t>字段"name:en"NULL值占比98.4%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1054,7 +1052,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>字段"name:en"NULL值占比98.4%</t>
+          <t>字段"addr:housename"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1077,7 +1075,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>字段"addr:housename"NULL值占比100.0%</t>
+          <t>字段"addr:postcode"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1100,7 +1098,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>字段"addr:postcode"NULL值占比99.6%</t>
+          <t>字段"addr:street"NULL值占比96.8%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1123,7 +1121,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>字段"addr:street"NULL值占比96.8%</t>
+          <t>字段"network"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1146,7 +1144,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>字段"network"NULL值占比100.0%</t>
+          <t>字段"public_transport"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1169,7 +1167,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>字段"public_transport"NULL值占比99.9%</t>
+          <t>字段"railway"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1192,7 +1190,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>字段"railway"NULL值占比100.0%</t>
+          <t>字段"station"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1215,7 +1213,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>字段"station"NULL值占比100.0%</t>
+          <t>字段"subway"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1238,7 +1236,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>字段"subway"NULL值占比100.0%</t>
+          <t>字段"wheelchair"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1261,7 +1259,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>字段"wheelchair"NULL值占比99.8%</t>
+          <t>字段"addr:housenumber"NULL值占比96.5%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1284,7 +1282,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>字段"addr:housenumber"NULL值占比96.5%</t>
+          <t>字段"building:levels"NULL值占比91.3%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1307,7 +1305,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>字段"building:levels"NULL值占比91.3%</t>
+          <t>字段"heritage"NULL值占比99.3%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1330,7 +1328,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>字段"heritage"NULL值占比99.3%</t>
+          <t>字段"heritage:operator"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1353,7 +1351,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>字段"heritage:operator"NULL值占比99.4%</t>
+          <t>字段"heritage:ref"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1376,7 +1374,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>字段"heritage:ref"NULL值占比99.4%</t>
+          <t>字段"old_name"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1399,7 +1397,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>字段"old_name"NULL值占比99.6%</t>
+          <t>字段"ref"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1422,7 +1420,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>字段"ref"NULL值占比99.9%</t>
+          <t>字段"addr:country"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1445,7 +1443,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>字段"addr:country"NULL值占比100.0%</t>
+          <t>字段"ref:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1468,7 +1466,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>字段"ref:zh"NULL值占比100.0%</t>
+          <t>字段"start_date"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1491,7 +1489,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>字段"start_date"NULL值占比99.4%</t>
+          <t>字段"addr:city"NULL值占比99.0%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1514,7 +1512,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>字段"addr:city"NULL值占比99.0%</t>
+          <t>字段"addr:province"NULL值占比98.4%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1537,7 +1535,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>字段"addr:province"NULL值占比98.4%</t>
+          <t>字段"description"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1560,7 +1558,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>字段"description"NULL值占比100.0%</t>
+          <t>字段"military"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1583,7 +1581,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>字段"military"NULL值占比100.0%</t>
+          <t>字段"source"NULL值占比95.8%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1606,7 +1604,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>字段"source"NULL值占比95.8%</t>
+          <t>字段"tourism"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1629,7 +1627,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>字段"tourism"NULL值占比99.6%</t>
+          <t>字段"addr:district"NULL值占比98.4%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1652,7 +1650,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>字段"addr:district"NULL值占比98.4%</t>
+          <t>字段"alt_name:ja"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1675,7 +1673,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>字段"alt_name:ja"NULL值占比100.0%</t>
+          <t>字段"building:material"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1698,7 +1696,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>字段"building:material"NULL值占比100.0%</t>
+          <t>字段"building:use"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1721,7 +1719,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>字段"building:use"NULL值占比100.0%</t>
+          <t>字段"check_date"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1744,7 +1742,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>字段"check_date"NULL值占比100.0%</t>
+          <t>字段"height"NULL值占比99.2%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1767,7 +1765,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>字段"height"NULL值占比99.2%</t>
+          <t>字段"name:ar"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1790,7 +1788,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>字段"name:ar"NULL值占比100.0%</t>
+          <t>字段"name:es"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1813,7 +1811,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>字段"name:es"NULL值占比100.0%</t>
+          <t>字段"name:fr"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1836,7 +1834,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>字段"name:fr"NULL值占比100.0%</t>
+          <t>字段"name:hi"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1859,7 +1857,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>字段"name:hi"NULL值占比100.0%</t>
+          <t>字段"name:ja"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1882,7 +1880,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>字段"name:ja"NULL值占比100.0%</t>
+          <t>字段"name:ja-Hira"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1905,7 +1903,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>字段"name:ja-Hira"NULL值占比100.0%</t>
+          <t>字段"name:ko"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1928,7 +1926,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>字段"name:ko"NULL值占比100.0%</t>
+          <t>字段"name:ru"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1951,7 +1949,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>字段"name:ru"NULL值占比99.9%</t>
+          <t>字段"name:th"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1974,7 +1972,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>字段"name:th"NULL值占比100.0%</t>
+          <t>字段"name:vi"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1997,7 +1995,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>字段"name:vi"NULL值占比100.0%</t>
+          <t>字段"name:wuu"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2020,7 +2018,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>字段"name:wuu"NULL值占比100.0%</t>
+          <t>字段"name:yue"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2043,7 +2041,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>字段"name:yue"NULL值占比100.0%</t>
+          <t>字段"name:zh-Latn-pinyin"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2066,7 +2064,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>字段"name:zh-Latn-pinyin"NULL值占比100.0%</t>
+          <t>字段"short_name"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2089,7 +2087,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>字段"short_name"NULL值占比100.0%</t>
+          <t>字段"website"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2112,7 +2110,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>字段"website"NULL值占比99.9%</t>
+          <t>字段"wikidata"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2135,7 +2133,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>字段"wikidata"NULL值占比99.7%</t>
+          <t>字段"wikimedia_commons"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2158,7 +2156,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>字段"wikimedia_commons"NULL值占比99.9%</t>
+          <t>字段"wikipedia"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2181,7 +2179,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>字段"wikipedia"NULL值占比99.8%</t>
+          <t>字段"brand"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2204,7 +2202,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>字段"brand"NULL值占比99.8%</t>
+          <t>字段"brand:en"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2227,7 +2225,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>字段"brand:en"NULL值占比99.9%</t>
+          <t>字段"brand:wikidata"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2250,7 +2248,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>字段"brand:wikidata"NULL值占比99.8%</t>
+          <t>字段"brand:wikipedia"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2273,7 +2271,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>字段"brand:wikipedia"NULL值占比99.9%</t>
+          <t>字段"brand:zh"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2296,7 +2294,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>字段"brand:zh"NULL值占比99.9%</t>
+          <t>字段"historic"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2319,7 +2317,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>字段"historic"NULL值占比99.9%</t>
+          <t>字段"addr:street:en"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2342,7 +2340,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>字段"addr:street:en"NULL值占比99.9%</t>
+          <t>字段"built"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2365,7 +2363,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>字段"built"NULL值占比100.0%</t>
+          <t>字段"use"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2388,7 +2386,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>字段"use"NULL值占比100.0%</t>
+          <t>字段"landuse"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2411,7 +2409,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>字段"landuse"NULL值占比100.0%</t>
+          <t>字段"check_date:opening_hours"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2434,7 +2432,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>字段"check_date:opening_hours"NULL值占比100.0%</t>
+          <t>字段"consulate"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2457,7 +2455,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>字段"consulate"NULL值占比100.0%</t>
+          <t>字段"country"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2480,7 +2478,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>字段"country"NULL值占比100.0%</t>
+          <t>字段"diplomatic"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2503,7 +2501,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>字段"diplomatic"NULL值占比100.0%</t>
+          <t>字段"office"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2526,7 +2524,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>字段"office"NULL值占比99.6%</t>
+          <t>字段"opening_hours:signed"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2549,7 +2547,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>字段"opening_hours:signed"NULL值占比100.0%</t>
+          <t>字段"target"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2572,7 +2570,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>字段"target"NULL值占比100.0%</t>
+          <t>字段"leisure"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2595,7 +2593,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>字段"leisure"NULL值占比99.9%</t>
+          <t>字段"sport"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2618,7 +2616,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>字段"sport"NULL值占比100.0%</t>
+          <t>字段"layer"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2641,7 +2639,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>字段"layer"NULL值占比99.4%</t>
+          <t>字段"maxspeed"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2664,7 +2662,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>字段"maxspeed"NULL值占比100.0%</t>
+          <t>字段"name:de"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2687,7 +2685,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>字段"name:de"NULL值占比100.0%</t>
+          <t>字段"train"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2710,7 +2708,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>字段"train"NULL值占比100.0%</t>
+          <t>字段"architect"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2733,7 +2731,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>字段"architect"NULL值占比100.0%</t>
+          <t>字段"architect:wikidata"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2756,7 +2754,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>字段"architect:wikidata"NULL值占比100.0%</t>
+          <t>字段"phone"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2779,7 +2777,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>字段"phone"NULL值占比99.9%</t>
+          <t>字段"fee"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2802,7 +2800,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>字段"fee"NULL值占比100.0%</t>
+          <t>字段"opening_hours"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2825,7 +2823,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>字段"opening_hours"NULL值占比99.9%</t>
+          <t>字段"museum"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2848,7 +2846,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>字段"museum"NULL值占比100.0%</t>
+          <t>字段"communication:radio"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2871,7 +2869,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>字段"communication:radio"NULL值占比100.0%</t>
+          <t>字段"communication:television"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2894,7 +2892,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>字段"communication:television"NULL值占比100.0%</t>
+          <t>字段"man_made"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2917,7 +2915,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>字段"man_made"NULL值占比100.0%</t>
+          <t>字段"name:pt"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2940,7 +2938,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>字段"name:pt"NULL值占比100.0%</t>
+          <t>字段"official_name"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2963,7 +2961,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>字段"official_name"NULL值占比100.0%</t>
+          <t>字段"operational_status"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2986,7 +2984,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>字段"operational_status"NULL值占比100.0%</t>
+          <t>字段"tourism:level:CN"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3009,7 +3007,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>字段"tourism:level:CN"NULL值占比100.0%</t>
+          <t>字段"tower:type"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3032,7 +3030,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>字段"tower:type"NULL值占比100.0%</t>
+          <t>字段"wikipedia:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3055,7 +3053,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>字段"wikipedia:en"NULL值占比100.0%</t>
+          <t>字段"contact:instagram"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3078,7 +3076,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>字段"contact:instagram"NULL值占比100.0%</t>
+          <t>字段"shop"NULL值占比99.5%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3101,7 +3099,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>字段"shop"NULL值占比99.5%</t>
+          <t>字段"alt_name:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3124,7 +3122,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>字段"alt_name:en"NULL值占比100.0%</t>
+          <t>字段"covered"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3147,7 +3145,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>字段"covered"NULL值占比100.0%</t>
+          <t>字段"bridge"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3170,7 +3168,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>字段"bridge"NULL值占比100.0%</t>
+          <t>字段"old_name:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3193,7 +3191,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>字段"old_name:en"NULL值占比100.0%</t>
+          <t>字段"internet_access"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3216,7 +3214,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>字段"internet_access"NULL值占比100.0%</t>
+          <t>字段"alt_name"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3239,7 +3237,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>字段"alt_name"NULL值占比99.9%</t>
+          <t>字段"name:uk"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3262,7 +3260,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>字段"name:uk"NULL值占比100.0%</t>
+          <t>字段"roof:shape"NULL值占比99.0%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3285,7 +3283,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>字段"roof:shape"NULL值占比99.0%</t>
+          <t>字段"smoking"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3308,7 +3306,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>字段"smoking"NULL值占比99.9%</t>
+          <t>字段"rooms"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3331,7 +3329,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>字段"rooms"NULL值占比100.0%</t>
+          <t>字段"area"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3354,7 +3352,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>字段"area"NULL值占比100.0%</t>
+          <t>字段"network:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3377,7 +3375,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>字段"network:en"NULL值占比100.0%</t>
+          <t>字段"network:wikidata"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3400,7 +3398,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>字段"network:wikidata"NULL值占比100.0%</t>
+          <t>字段"network:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3423,7 +3421,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>字段"network:zh"NULL值占比100.0%</t>
+          <t>字段"int_name"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3446,7 +3444,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>字段"int_name"NULL值占比99.9%</t>
+          <t>字段"building:colour"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3469,7 +3467,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>字段"building:colour"NULL值占比99.8%</t>
+          <t>字段"min_height"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3492,7 +3490,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>字段"min_height"NULL值占比100.0%</t>
+          <t>字段"roof:colour"NULL值占比99.1%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3515,7 +3513,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>字段"roof:colour"NULL值占比99.1%</t>
+          <t>字段"emergency"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3538,7 +3536,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>字段"emergency"NULL值占比100.0%</t>
+          <t>字段"healthcare"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3561,7 +3559,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>字段"healthcare"NULL值占比100.0%</t>
+          <t>字段"roof:levels"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3584,7 +3582,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>字段"roof:levels"NULL值占比99.8%</t>
+          <t>字段"cuisine"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3607,7 +3605,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>字段"cuisine"NULL值占比100.0%</t>
+          <t>字段"diet:chicken"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3630,7 +3628,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>字段"diet:chicken"NULL值占比100.0%</t>
+          <t>字段"diet:fish"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -3653,7 +3651,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>字段"diet:fish"NULL值占比100.0%</t>
+          <t>字段"diet:healthy"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3676,7 +3674,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>字段"diet:healthy"NULL值占比100.0%</t>
+          <t>字段"diet:local"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -3699,7 +3697,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>字段"diet:local"NULL值占比100.0%</t>
+          <t>字段"diet:meat"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3722,7 +3720,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>字段"diet:meat"NULL值占比100.0%</t>
+          <t>字段"building:levels:underground"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -3745,7 +3743,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>字段"building:levels:underground"NULL值占比99.9%</t>
+          <t>字段"religion"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -3768,7 +3766,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>字段"religion"NULL值占比99.9%</t>
+          <t>字段"theatre:type"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -3791,7 +3789,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>字段"theatre:type"NULL值占比100.0%</t>
+          <t>字段"denomination"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -3814,7 +3812,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>字段"denomination"NULL值占比100.0%</t>
+          <t>字段"service_times"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -3837,7 +3835,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>字段"service_times"NULL值占比100.0%</t>
+          <t>字段"studio"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -3860,7 +3858,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>字段"studio"NULL值占比100.0%</t>
+          <t>字段"internet_access:fee"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -3883,7 +3881,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>字段"internet_access:fee"NULL值占比100.0%</t>
+          <t>字段"operator"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -3906,7 +3904,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>字段"operator"NULL值占比99.9%</t>
+          <t>字段"contact:bilibili"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -3929,7 +3927,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>字段"contact:bilibili"NULL值占比100.0%</t>
+          <t>字段"contact:phone"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -3952,7 +3950,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>字段"contact:phone"NULL值占比100.0%</t>
+          <t>字段"contact:tiktok"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -3975,7 +3973,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>字段"contact:tiktok"NULL值占比100.0%</t>
+          <t>字段"contact:twitter"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -3998,7 +3996,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>字段"contact:twitter"NULL值占比100.0%</t>
+          <t>字段"contact:weibo"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -4021,7 +4019,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>字段"contact:weibo"NULL值占比100.0%</t>
+          <t>字段"contact:youtube"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4044,7 +4042,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>字段"contact:youtube"NULL值占比100.0%</t>
+          <t>字段"toilets:wheelchair"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4067,7 +4065,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>字段"toilets:wheelchair"NULL值占比100.0%</t>
+          <t>字段"website:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4090,7 +4088,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>字段"website:en"NULL值占比100.0%</t>
+          <t>字段"bus"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4113,7 +4111,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>字段"bus"NULL值占比100.0%</t>
+          <t>字段"image"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4136,7 +4134,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>字段"image"NULL值占比100.0%</t>
+          <t>字段"name:bn"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4159,7 +4157,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>字段"name:bn"NULL值占比100.0%</t>
+          <t>字段"name:id"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4182,7 +4180,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>字段"name:id"NULL值占比100.0%</t>
+          <t>字段"name:ml"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4205,7 +4203,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>字段"name:ml"NULL值占比100.0%</t>
+          <t>字段"name:tr"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4228,7 +4226,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>字段"name:tr"NULL值占比100.0%</t>
+          <t>字段"addr:housename:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4251,7 +4249,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>字段"addr:housename:en"NULL值占比100.0%</t>
+          <t>字段"parking"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -4274,7 +4272,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>字段"parking"NULL值占比100.0%</t>
+          <t>字段"source:name"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4297,7 +4295,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>字段"source:name"NULL值占比100.0%</t>
+          <t>字段"addr:housenumber:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4320,7 +4318,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>字段"addr:housenumber:en"NULL值占比100.0%</t>
+          <t>字段"power"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4343,7 +4341,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>字段"power"NULL值占比100.0%</t>
+          <t>字段"alt_name:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4366,7 +4364,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>字段"alt_name:zh"NULL值占比100.0%</t>
+          <t>字段"length"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4389,7 +4387,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>字段"length"NULL值占比100.0%</t>
+          <t>字段"width"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4412,7 +4410,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>字段"width"NULL值占比100.0%</t>
+          <t>字段"air_conditioning"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4435,7 +4433,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>字段"air_conditioning"NULL值占比100.0%</t>
+          <t>字段"stars"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4458,7 +4456,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>字段"stars"NULL值占比100.0%</t>
+          <t>字段"contact:email"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4481,7 +4479,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>字段"contact:email"NULL值占比100.0%</t>
+          <t>字段"contact:website"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -4504,7 +4502,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>字段"contact:website"NULL值占比100.0%</t>
+          <t>字段"ferry"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4527,7 +4525,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>字段"ferry"NULL值占比100.0%</t>
+          <t>字段"museum_type"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4550,7 +4548,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>字段"museum_type"NULL值占比100.0%</t>
+          <t>字段"toilets"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -4573,7 +4571,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>字段"toilets"NULL值占比100.0%</t>
+          <t>字段"charge"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -4596,7 +4594,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>字段"charge"NULL值占比100.0%</t>
+          <t>字段"name:he"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -4619,7 +4617,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>字段"name:he"NULL值占比100.0%</t>
+          <t>字段"level"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -4642,7 +4640,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>字段"level"NULL值占比100.0%</t>
+          <t>字段"location"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -4665,7 +4663,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>字段"location"NULL值占比100.0%</t>
+          <t>字段"payment:alipay"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -4688,7 +4686,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>字段"payment:alipay"NULL值占比100.0%</t>
+          <t>字段"payment:american_express"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -4711,7 +4709,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>字段"payment:american_express"NULL值占比100.0%</t>
+          <t>字段"payment:apple_pay"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -4734,7 +4732,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>字段"payment:apple_pay"NULL值占比100.0%</t>
+          <t>字段"payment:cash"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -4757,7 +4755,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>字段"payment:cash"NULL值占比100.0%</t>
+          <t>字段"payment:credit_cards"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -4780,7 +4778,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>字段"payment:credit_cards"NULL值占比100.0%</t>
+          <t>字段"payment:discover_card"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -4803,7 +4801,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>字段"payment:discover_card"NULL值占比100.0%</t>
+          <t>字段"payment:huawei_pay"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -4826,7 +4824,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>字段"payment:huawei_pay"NULL值占比100.0%</t>
+          <t>字段"payment:mastercard"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -4849,7 +4847,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>字段"payment:mastercard"NULL值占比100.0%</t>
+          <t>字段"payment:mipay"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -4872,7 +4870,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>字段"payment:mipay"NULL值占比100.0%</t>
+          <t>字段"payment:samsung_pay"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -4895,7 +4893,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>字段"payment:samsung_pay"NULL值占比100.0%</t>
+          <t>字段"payment:unionpay"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -4918,7 +4916,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>字段"payment:unionpay"NULL值占比100.0%</t>
+          <t>字段"payment:visa"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -4941,7 +4939,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>字段"payment:visa"NULL值占比100.0%</t>
+          <t>字段"aeroway"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -4964,7 +4962,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>字段"aeroway"NULL值占比100.0%</t>
+          <t>字段"disused"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -4987,7 +4985,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>字段"disused"NULL值占比100.0%</t>
+          <t>字段"disused:aeroway"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5010,7 +5008,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>字段"disused:aeroway"NULL值占比100.0%</t>
+          <t>字段"roof:orientation"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5033,7 +5031,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>字段"roof:orientation"NULL值占比100.0%</t>
+          <t>字段"cinema:cinity"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5056,7 +5054,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>字段"cinema:cinity"NULL值占比100.0%</t>
+          <t>字段"cinema:dolby_atmos"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5079,7 +5077,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>字段"cinema:dolby_atmos"NULL值占比100.0%</t>
+          <t>字段"cinema:dolby_cinema"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5102,7 +5100,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>字段"cinema:dolby_cinema"NULL值占比100.0%</t>
+          <t>字段"cinema:onyx"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5125,7 +5123,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>字段"cinema:onyx"NULL值占比100.0%</t>
+          <t>字段"cinema:realD"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5148,7 +5146,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>字段"cinema:realD"NULL值占比100.0%</t>
+          <t>字段"dsscreated"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5171,7 +5169,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>字段"dsscreated"NULL值占比100.0%</t>
+          <t>字段"screen"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5194,7 +5192,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>字段"screen"NULL值占比100.0%</t>
+          <t>字段"access"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5217,7 +5215,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>字段"access"NULL值占比100.0%</t>
+          <t>字段"internet_access:ssid"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -5240,7 +5238,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>字段"internet_access:ssid"NULL值占比100.0%</t>
+          <t>字段"addr:city:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -5263,7 +5261,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>字段"addr:city:en"NULL值占比100.0%</t>
+          <t>字段"email"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -5286,7 +5284,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>字段"email"NULL值占比100.0%</t>
+          <t>字段"fax"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -5309,7 +5307,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>字段"fax"NULL值占比100.0%</t>
+          <t>字段"education"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -5332,7 +5330,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>字段"education"NULL值占比100.0%</t>
+          <t>字段"frequency"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5355,7 +5353,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>字段"frequency"NULL值占比100.0%</t>
+          <t>字段"substation"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -5378,7 +5376,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>字段"substation"NULL值占比100.0%</t>
+          <t>字段"capacity:disabled"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -5401,7 +5399,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>字段"capacity:disabled"NULL值占比100.0%</t>
+          <t>字段"atm"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -5424,7 +5422,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>字段"atm"NULL值占比100.0%</t>
+          <t>字段"community_centre"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -5447,7 +5445,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>字段"community_centre"NULL值占比100.0%</t>
+          <t>字段"government"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -5470,7 +5468,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>字段"government"NULL值占比100.0%</t>
+          <t>字段"construction:leisure"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -5493,7 +5491,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>字段"construction:leisure"NULL值占比100.0%</t>
+          <t>字段"opening_date"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -5516,7 +5514,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>字段"opening_date"NULL值占比100.0%</t>
+          <t>字段"short_name:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -5539,7 +5537,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>字段"short_name:en"NULL值占比100.0%</t>
+          <t>字段"construction"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -5562,7 +5560,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>字段"construction"NULL值占比100.0%</t>
+          <t>字段"nohousenumber"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -5585,7 +5583,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>字段"nohousenumber"NULL值占比100.0%</t>
+          <t>字段"roof:direction"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -5608,7 +5606,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>字段"roof:direction"NULL值占比100.0%</t>
+          <t>字段"roof:height"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -5631,7 +5629,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>字段"roof:height"NULL值占比99.9%</t>
+          <t>字段"roof:material"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -5654,7 +5652,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>字段"roof:material"NULL值占比100.0%</t>
+          <t>字段"website:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -5677,7 +5675,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>字段"website:zh"NULL值占比100.0%</t>
+          <t>字段"elevator"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -5700,7 +5698,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>字段"elevator"NULL值占比100.0%</t>
+          <t>字段"colour"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -5723,7 +5721,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>字段"colour"NULL值占比100.0%</t>
+          <t>字段"fast_food"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -5746,7 +5744,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>字段"fast_food"NULL值占比100.0%</t>
+          <t>字段"attraction"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -5769,7 +5767,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>字段"attraction"NULL值占比100.0%</t>
+          <t>字段"female"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -5792,7 +5790,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>字段"female"NULL值占比100.0%</t>
+          <t>字段"male"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -5815,7 +5813,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>字段"male"NULL值占比100.0%</t>
+          <t>字段"toilets:disposal"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -5838,7 +5836,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>字段"toilets:disposal"NULL值占比100.0%</t>
+          <t>字段"theatre"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -5861,7 +5859,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>字段"theatre"NULL值占比100.0%</t>
+          <t>字段"social_facility"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -5884,7 +5882,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>字段"social_facility"NULL值占比100.0%</t>
+          <t>字段"social_facility:for"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -5907,7 +5905,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>字段"social_facility:for"NULL值占比100.0%</t>
+          <t>字段"name:yue-Hant"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -5930,7 +5928,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>字段"name:yue-Hant"NULL值占比100.0%</t>
+          <t>字段"school"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -5953,7 +5951,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>字段"school"NULL值占比100.0%</t>
+          <t>字段"bench"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -5976,7 +5974,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>字段"bench"NULL值占比100.0%</t>
+          <t>字段"shelter_type"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -5999,7 +5997,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>字段"shelter_type"NULL值占比100.0%</t>
+          <t>字段"name:it"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -6022,7 +6020,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>字段"name:it"NULL值占比100.0%</t>
+          <t>字段"name:zh-Hans-CN"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -6045,7 +6043,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>字段"name:zh-Hans-CN"NULL值占比100.0%</t>
+          <t>字段"name:zh-Hant-CN"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -6068,7 +6066,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>字段"name:zh-Hant-CN"NULL值占比100.0%</t>
+          <t>字段"swimming_pool"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -6091,7 +6089,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>字段"swimming_pool"NULL值占比100.0%</t>
+          <t>字段"wall"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -6114,7 +6112,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>字段"wall"NULL值占比100.0%</t>
+          <t>字段"shop_1"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -6137,7 +6135,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>字段"shop_1"NULL值占比100.0%</t>
+          <t>字段"shop_2"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -6160,7 +6158,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>字段"shop_2"NULL值占比100.0%</t>
+          <t>字段"ele"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -6183,7 +6181,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>字段"ele"NULL值占比99.8%</t>
+          <t>字段"wikipedia:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -6206,7 +6204,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>字段"wikipedia:zh"NULL值占比100.0%</t>
+          <t>字段"tower"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -6229,7 +6227,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>字段"tower"NULL值占比100.0%</t>
+          <t>字段"building:part"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -6252,7 +6250,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>字段"building:part"NULL值占比100.0%</t>
+          <t>字段"old_name:fr"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -6275,7 +6273,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>字段"old_name:fr"NULL值占比100.0%</t>
+          <t>字段"source:architect"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -6298,7 +6296,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>字段"source:architect"NULL值占比100.0%</t>
+          <t>字段"source:heritage:ref"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -6321,7 +6319,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>字段"source:heritage:ref"NULL值占比100.0%</t>
+          <t>字段"was:building:levels"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -6344,7 +6342,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>字段"was:building:levels"NULL值占比100.0%</t>
+          <t>字段"boundary"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -6367,7 +6365,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>字段"boundary"NULL值占比100.0%</t>
+          <t>字段"protect_class"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -6390,7 +6388,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>字段"protect_class"NULL值占比100.0%</t>
+          <t>字段"building:min_level"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -6413,7 +6411,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>字段"building:min_level"NULL值占比100.0%</t>
+          <t>字段"relation"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -6436,7 +6434,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>字段"relation"NULL值占比100.0%</t>
+          <t>字段"alt_name:de"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -6459,7 +6457,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>字段"alt_name:de"NULL值占比100.0%</t>
+          <t>字段"alt_name:fr"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -6482,7 +6480,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>字段"alt_name:fr"NULL值占比100.0%</t>
+          <t>字段"alt_name:nl"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -6505,7 +6503,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>字段"alt_name:nl"NULL值占比100.0%</t>
+          <t>字段"name:nl"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -6528,7 +6526,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>字段"name:nl"NULL值占比100.0%</t>
+          <t>字段"fixme"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -6551,7 +6549,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>字段"fixme"NULL值占比100.0%</t>
+          <t>字段"club"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -6574,7 +6572,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>字段"club"NULL值占比100.0%</t>
+          <t>字段"library"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -6597,7 +6595,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>字段"library"NULL值占比100.0%</t>
+          <t>字段"addr:alley"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -6620,7 +6618,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>字段"addr:alley"NULL值占比100.0%</t>
+          <t>字段"drive_through"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -6643,7 +6641,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>字段"drive_through"NULL值占比100.0%</t>
+          <t>字段"bath:open_air"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -6666,7 +6664,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>字段"bath:open_air"NULL值占比100.0%</t>
+          <t>字段"fuel:octane_92"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -6689,7 +6687,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>字段"fuel:octane_92"NULL值占比100.0%</t>
+          <t>字段"fuel:octane_95"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -6712,7 +6710,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>字段"fuel:octane_95"NULL值占比100.0%</t>
+          <t>字段"fuel:octane_98"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -6735,7 +6733,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>字段"fuel:octane_98"NULL值占比100.0%</t>
+          <t>字段"building:flats"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -6758,7 +6756,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>字段"building:flats"NULL值占比100.0%</t>
+          <t>字段"indoor"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -6781,7 +6779,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>字段"indoor"NULL值占比100.0%</t>
+          <t>字段"not:name"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -6804,7 +6802,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>字段"not:name"NULL值占比100.0%</t>
+          <t>字段"building_1"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -6827,7 +6825,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>字段"building_1"NULL值占比100.0%</t>
+          <t>字段"temporary"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -6850,7 +6848,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>字段"temporary"NULL值占比100.0%</t>
+          <t>字段"old_name_1"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -6873,7 +6871,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>字段"old_name_1"NULL值占比100.0%</t>
+          <t>字段"contact:wechat"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -6896,7 +6894,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>字段"contact:wechat"NULL值占比100.0%</t>
+          <t>字段"was:building"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -6919,7 +6917,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>字段"was:building"NULL值占比100.0%</t>
+          <t>字段"generator:source"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -6942,7 +6940,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>字段"generator:source"NULL值占比100.0%</t>
+          <t>字段"addr:suburb"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -6965,7 +6963,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>字段"addr:suburb"NULL值占比100.0%</t>
+          <t>字段"industrial"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -6988,7 +6986,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>字段"industrial"NULL值占比100.0%</t>
+          <t>字段"bar"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -7011,7 +7009,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>字段"bar"NULL值占比100.0%</t>
+          <t>字段"reservation"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -7034,7 +7032,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>字段"reservation"NULL值占比100.0%</t>
+          <t>字段"operator:type"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -7057,7 +7055,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>字段"operator:type"NULL值占比100.0%</t>
+          <t>字段"payment:wechat"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -7080,7 +7078,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>字段"payment:wechat"NULL值占比100.0%</t>
+          <t>字段"abandoned"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -7103,7 +7101,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>字段"abandoned"NULL值占比100.0%</t>
+          <t>字段"bicycle_parking"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -7126,7 +7124,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>字段"bicycle_parking"NULL值占比100.0%</t>
+          <t>字段"operator:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -7149,7 +7147,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>字段"operator:en"NULL值占比100.0%</t>
+          <t>字段"operator:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -7172,7 +7170,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>字段"operator:zh"NULL值占比100.0%</t>
+          <t>字段"access:covid19"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -7195,7 +7193,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>字段"access:covid19"NULL值占比100.0%</t>
+          <t>字段"not:brand:wikidata"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -7218,7 +7216,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>字段"not:brand:wikidata"NULL值占比100.0%</t>
+          <t>字段"disused:shop"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -7241,7 +7239,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>字段"disused:shop"NULL值占比100.0%</t>
+          <t>字段"internet_access:password"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -7264,7 +7262,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>字段"internet_access:password"NULL值占比100.0%</t>
+          <t>字段"changing_table"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -7287,7 +7285,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>字段"changing_table"NULL值占比100.0%</t>
+          <t>字段"unisex"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -7310,7 +7308,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>字段"unisex"NULL值占比100.0%</t>
+          <t>字段"ruins"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -7333,7 +7331,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>字段"ruins"NULL值占比100.0%</t>
+          <t>字段"residential"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -7356,7 +7354,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>字段"residential"NULL值占比100.0%</t>
+          <t>字段"university"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -7379,7 +7377,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>字段"university"NULL值占比100.0%</t>
+          <t>字段"townhall:type"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -7402,7 +7400,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>字段"townhall:type"NULL值占比100.0%</t>
+          <t>字段"depot"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -7425,7 +7423,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>字段"depot"NULL值占比100.0%</t>
+          <t>字段"name:ms"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -7448,7 +7446,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>字段"name:ms"NULL值占比100.0%</t>
+          <t>字段"cinema:3D"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -7471,7 +7469,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>字段"cinema:3D"NULL值占比100.0%</t>
+          <t>字段"takeaway"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -7494,7 +7492,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>字段"takeaway"NULL值占比100.0%</t>
+          <t>字段"old_name:1952-2018"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -7517,7 +7515,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>字段"old_name:1952-2018"NULL值占比100.0%</t>
+          <t>字段"was:amenity"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -7540,7 +7538,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>字段"was:amenity"NULL值占比100.0%</t>
+          <t>字段"fuel:diesel"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -7563,7 +7561,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>字段"fuel:diesel"NULL值占比100.0%</t>
+          <t>字段"self_service"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -7586,7 +7584,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>字段"self_service"NULL值占比100.0%</t>
+          <t>字段"information"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -7609,7 +7607,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>字段"information"NULL值占比100.0%</t>
+          <t>字段"outdoor_seating"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -7632,7 +7630,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>字段"outdoor_seating"NULL值占比100.0%</t>
+          <t>字段"service:vehicle:car_repair"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -7655,7 +7653,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>字段"service:vehicle:car_repair"NULL值占比100.0%</t>
+          <t>字段"service:vehicle:new_car_sales"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -7678,7 +7676,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>字段"service:vehicle:new_car_sales"NULL值占比100.0%</t>
+          <t>字段"bin"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -7701,7 +7699,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>字段"bin"NULL值占比100.0%</t>
+          <t>字段"addr:flats"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -7724,7 +7722,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>字段"addr:flats"NULL值占比100.0%</t>
+          <t>字段"second_hand"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -7747,7 +7745,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>字段"second_hand"NULL值占比100.0%</t>
+          <t>字段"addr:unit"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -7770,7 +7768,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>字段"addr:unit"NULL值占比100.0%</t>
+          <t>字段"addr:floor"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -7793,7 +7791,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>字段"addr:floor"NULL值占比100.0%</t>
+          <t>字段"was:ferry"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -7816,7 +7814,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>字段"was:ferry"NULL值占比100.0%</t>
+          <t>字段"was:public_transport"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -7839,7 +7837,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>字段"was:public_transport"NULL值占比100.0%</t>
+          <t>字段"lit"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -7862,7 +7860,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>字段"lit"NULL值占比100.0%</t>
+          <t>字段"admin_level"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
@@ -7885,7 +7883,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>字段"admin_level"NULL值占比100.0%</t>
+          <t>字段"construction_date"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
@@ -7908,7 +7906,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>字段"construction_date"NULL值占比100.0%</t>
+          <t>字段"voltage"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
@@ -7931,7 +7929,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>字段"voltage"NULL值占比100.0%</t>
+          <t>字段"type"NULL值占比99.2%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -7954,7 +7952,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>字段"type"NULL值占比99.2%</t>
+          <t>字段"entrance"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
@@ -7977,7 +7975,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>字段"entrance"NULL值占比100.0%</t>
+          <t>字段"source_1"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
@@ -8000,7 +7998,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>字段"source_1"NULL值占比100.0%</t>
+          <t>字段"contact:facebook"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
@@ -8013,47 +8011,47 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>NULL比例</t>
+          <t>域值范围</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>字段"contact:facebook"NULL值占比100.0%</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr"/>
+          <t>字段"building"有48个非法值</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>['residential', 'bunker', 'university', 'roof', 'stadium', 'kindergarten', 'yes;roof', 'retail;commercial', 'apartments;residential', 'commercial;yes']</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>shanghai_buildings.geojson</t>
+          <t>shanghai_poi.geojson</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>域值范围</t>
+          <t>NULL比例</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>字段"building"有48个非法值</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>['residential', 'bunker', 'university', 'roof', 'stadium', 'kindergarten', 'yes;roof', 'retail;commercial', 'apartments;residential', 'commercial;yes']</t>
-        </is>
-      </c>
+          <t>字段"addr:housename"NULL值占比99.9%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8073,7 +8071,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>字段"addr:housename"NULL值占比99.9%</t>
+          <t>字段"addr:postcode"NULL值占比98.0%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -8096,7 +8094,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>字段"addr:postcode"NULL值占比98.0%</t>
+          <t>字段"addr:street"NULL值占比79.0%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -8119,7 +8117,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>字段"addr:street"NULL值占比79.0%</t>
+          <t>字段"addr:city"NULL值占比86.5%</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -8142,7 +8140,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>字段"addr:city"NULL值占比86.5%</t>
+          <t>字段"addr:housenumber"NULL值占比81.1%</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
@@ -8165,7 +8163,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>字段"addr:housenumber"NULL值占比81.1%</t>
+          <t>字段"name:de"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
@@ -8188,7 +8186,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>字段"name:de"NULL值占比99.4%</t>
+          <t>字段"name:en"NULL值占比71.5%</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -8211,7 +8209,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>字段"name:en"NULL值占比71.5%</t>
+          <t>字段"name:zh"NULL值占比88.5%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -8234,7 +8232,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>字段"name:zh"NULL值占比88.5%</t>
+          <t>字段"website"NULL值占比98.0%</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -8257,7 +8255,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>字段"website"NULL值占比98.0%</t>
+          <t>字段"education"NULL值占比97.3%</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -8280,7 +8278,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>字段"education"NULL值占比97.3%</t>
+          <t>字段"name:fr"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -8303,7 +8301,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>字段"name:fr"NULL值占比99.8%</t>
+          <t>字段"wheelchair"NULL值占比93.6%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -8326,7 +8324,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>字段"wheelchair"NULL值占比93.6%</t>
+          <t>字段"name:zh-Hant"NULL值占比97.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
@@ -8349,7 +8347,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>字段"name:zh-Hant"NULL值占比97.2%</t>
+          <t>字段"level"NULL值占比94.3%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
@@ -8372,7 +8370,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>字段"level"NULL值占比94.3%</t>
+          <t>字段"int_name"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
@@ -8395,7 +8393,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>字段"int_name"NULL值占比99.9%</t>
+          <t>字段"alt_name"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
@@ -8418,7 +8416,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>字段"alt_name"NULL值占比99.9%</t>
+          <t>字段"alt_name:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
@@ -8441,7 +8439,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>字段"alt_name:zh"NULL值占比100.0%</t>
+          <t>字段"phone"NULL值占比94.6%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
@@ -8464,7 +8462,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>字段"phone"NULL值占比94.6%</t>
+          <t>字段"wikidata"NULL值占比98.4%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -8487,7 +8485,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>字段"wikidata"NULL值占比98.4%</t>
+          <t>字段"wikimedia_commons"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
@@ -8510,7 +8508,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>字段"wikimedia_commons"NULL值占比99.6%</t>
+          <t>字段"wikipedia"NULL值占比98.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
@@ -8533,7 +8531,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>字段"wikipedia"NULL值占比98.9%</t>
+          <t>字段"building"NULL值占比98.1%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
@@ -8556,7 +8554,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>字段"building"NULL值占比98.1%</t>
+          <t>字段"name:zh-Hans"NULL值占比97.3%</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
@@ -8579,7 +8577,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>字段"name:zh-Hans"NULL值占比97.3%</t>
+          <t>字段"addr:district"NULL值占比96.4%</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
@@ -8602,7 +8600,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>字段"addr:district"NULL值占比96.4%</t>
+          <t>字段"addr:province"NULL值占比97.3%</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -8625,7 +8623,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>字段"addr:province"NULL值占比97.3%</t>
+          <t>字段"note"NULL值占比99.0%</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -8648,7 +8646,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>字段"note"NULL值占比99.0%</t>
+          <t>字段"old_name"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -8671,7 +8669,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>字段"old_name"NULL值占比99.4%</t>
+          <t>字段"grades"NULL值占比99.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
@@ -8694,7 +8692,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>字段"grades"NULL值占比99.2%</t>
+          <t>字段"religion"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
@@ -8717,7 +8715,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>字段"religion"NULL值占比99.8%</t>
+          <t>字段"addr:city_1"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -8740,7 +8738,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>字段"addr:city_1"NULL值占比100.0%</t>
+          <t>字段"description"NULL值占比98.7%</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
@@ -8763,7 +8761,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>字段"description"NULL值占比98.7%</t>
+          <t>字段"operator"NULL值占比99.3%</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -8786,7 +8784,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>字段"operator"NULL值占比99.3%</t>
+          <t>字段"fee"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -8809,7 +8807,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>字段"fee"NULL值占比99.9%</t>
+          <t>字段"isced:level"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
@@ -8832,7 +8830,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>字段"isced:level"NULL值占比100.0%</t>
+          <t>字段"operator:type"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -8855,7 +8853,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>字段"operator:type"NULL值占比99.7%</t>
+          <t>字段"check_date"NULL值占比98.1%</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -8878,7 +8876,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>字段"check_date"NULL值占比98.1%</t>
+          <t>字段"email"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
@@ -8901,7 +8899,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>字段"email"NULL值占比99.6%</t>
+          <t>字段"barrier"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -8924,7 +8922,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>字段"barrier"NULL值占比100.0%</t>
+          <t>字段"type"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
@@ -8947,7 +8945,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>字段"type"NULL值占比99.7%</t>
+          <t>字段"healthcare"NULL值占比93.5%</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -8970,7 +8968,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>字段"healthcare"NULL值占比93.5%</t>
+          <t>字段"emergency"NULL值占比99.1%</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
@@ -8993,7 +8991,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>字段"emergency"NULL值占比99.1%</t>
+          <t>字段"source"NULL值占比99.0%</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -9016,7 +9014,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>字段"source"NULL值占比99.0%</t>
+          <t>字段"healthcare:speciality"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -9039,7 +9037,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>字段"healthcare:speciality"NULL值占比99.7%</t>
+          <t>字段"official_name"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -9062,7 +9060,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>字段"official_name"NULL值占比99.4%</t>
+          <t>字段"official_name:en"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -9085,7 +9083,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>字段"official_name:en"NULL值占比99.8%</t>
+          <t>字段"old_name:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -9108,7 +9106,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>字段"old_name:en"NULL值占比100.0%</t>
+          <t>字段"old_name:fr"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -9131,7 +9129,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>字段"old_name:fr"NULL值占比100.0%</t>
+          <t>字段"opening_hours"NULL值占比93.5%</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -9154,7 +9152,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>字段"opening_hours"NULL值占比93.5%</t>
+          <t>字段"landuse"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -9177,7 +9175,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>字段"landuse"NULL值占比99.9%</t>
+          <t>字段"area"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -9200,7 +9198,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>字段"area"NULL值占比100.0%</t>
+          <t>字段"building:levels"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -9223,7 +9221,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>字段"building:levels"NULL值占比99.7%</t>
+          <t>字段"beds"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -9246,7 +9244,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>字段"beds"NULL值占比100.0%</t>
+          <t>字段"short_name:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -9269,7 +9267,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>字段"short_name:en"NULL值占比100.0%</t>
+          <t>字段"short_name:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -9292,7 +9290,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>字段"short_name:zh"NULL值占比100.0%</t>
+          <t>字段"alt_name_1"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -9315,7 +9313,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>字段"alt_name_1"NULL值占比100.0%</t>
+          <t>字段"alt_name_2"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -9338,7 +9336,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>字段"alt_name_2"NULL值占比100.0%</t>
+          <t>字段"wikipedia:zh"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -9361,7 +9359,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>字段"wikipedia:zh"NULL值占比100.0%</t>
+          <t>字段"smoking"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -9384,7 +9382,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>字段"smoking"NULL值占比99.7%</t>
+          <t>字段"brand"NULL值占比95.1%</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -9407,7 +9405,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>字段"brand"NULL值占比95.1%</t>
+          <t>字段"brand:en"NULL值占比95.7%</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -9430,7 +9428,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>字段"brand:en"NULL值占比95.7%</t>
+          <t>字段"brand:wikidata"NULL值占比95.3%</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
@@ -9453,7 +9451,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>字段"brand:wikidata"NULL值占比95.3%</t>
+          <t>字段"brand:wikipedia"NULL值占比98.6%</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -9476,7 +9474,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>字段"brand:wikipedia"NULL值占比98.6%</t>
+          <t>字段"brand:zh"NULL值占比95.7%</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -9499,7 +9497,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>字段"brand:zh"NULL值占比95.7%</t>
+          <t>字段"cuisine"NULL值占比68.0%</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -9522,7 +9520,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>字段"cuisine"NULL值占比68.0%</t>
+          <t>字段"diet:vegan"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -9545,7 +9543,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>字段"diet:vegan"NULL值占比99.6%</t>
+          <t>字段"diet:vegetarian"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -9568,7 +9566,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>字段"diet:vegetarian"NULL值占比99.8%</t>
+          <t>字段"shop"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -9591,7 +9589,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>字段"shop"NULL值占比99.8%</t>
+          <t>字段"outdoor_seating"NULL值占比97.9%</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -9614,7 +9612,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>字段"outdoor_seating"NULL值占比97.9%</t>
+          <t>字段"name:ru"NULL值占比99.1%</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -9637,7 +9635,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>字段"name:ru"NULL值占比99.1%</t>
+          <t>字段"name:zh-Latn-pinyin"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -9660,7 +9658,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>字段"name:zh-Latn-pinyin"NULL值占比99.8%</t>
+          <t>字段"floor"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -9683,7 +9681,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>字段"floor"NULL值占比100.0%</t>
+          <t>字段"branch"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -9706,7 +9704,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>字段"branch"NULL值占比99.7%</t>
+          <t>字段"indoor_seating"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -9729,7 +9727,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>字段"indoor_seating"NULL值占比99.9%</t>
+          <t>字段"toilets:wheelchair"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -9752,7 +9750,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>字段"toilets:wheelchair"NULL值占比99.8%</t>
+          <t>字段"name:ko"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -9775,7 +9773,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>字段"name:ko"NULL值占比99.6%</t>
+          <t>字段"takeaway"NULL值占比99.4%</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -9798,7 +9796,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>字段"takeaway"NULL值占比99.4%</t>
+          <t>字段"capacity"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -9821,7 +9819,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>字段"capacity"NULL值占比99.8%</t>
+          <t>字段"name:ja"NULL值占比99.2%</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -9844,7 +9842,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>字段"name:ja"NULL值占比99.2%</t>
+          <t>字段"was:amenity"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -9867,7 +9865,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>字段"was:amenity"NULL值占比99.8%</t>
+          <t>字段"was:name"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -9890,7 +9888,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>字段"was:name"NULL值占比99.8%</t>
+          <t>字段"delivery"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -9913,7 +9911,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>字段"delivery"NULL值占比99.8%</t>
+          <t>字段"dsscreated"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -9936,7 +9934,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>字段"dsscreated"NULL值占比99.8%</t>
+          <t>字段"internet_access"NULL值占比98.5%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
@@ -9959,7 +9957,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>字段"internet_access"NULL值占比98.5%</t>
+          <t>字段"internet_access:fee"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -9982,7 +9980,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>字段"internet_access:fee"NULL值占比99.9%</t>
+          <t>字段"price"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -10005,7 +10003,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>字段"price"NULL值占比99.8%</t>
+          <t>字段"reservation"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -10028,7 +10026,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>字段"reservation"NULL值占比99.7%</t>
+          <t>字段"check_date:opening_hours"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -10051,7 +10049,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>字段"check_date:opening_hours"NULL值占比99.6%</t>
+          <t>字段"drive_in"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -10074,7 +10072,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>字段"drive_in"NULL值占比99.9%</t>
+          <t>字段"microbrewery"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -10097,7 +10095,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>字段"microbrewery"NULL值占比99.9%</t>
+          <t>字段"organic"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
@@ -10120,7 +10118,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>字段"organic"NULL值占比100.0%</t>
+          <t>字段"brand:ja"NULL值占比99.3%</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
@@ -10143,7 +10141,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>字段"brand:ja"NULL值占比99.3%</t>
+          <t>字段"brand:zh-Hans"NULL值占比99.5%</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -10166,7 +10164,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>字段"brand:zh-Hans"NULL值占比99.5%</t>
+          <t>字段"brand:zh-Hant"NULL值占比99.5%</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
@@ -10189,7 +10187,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>字段"brand:zh-Hant"NULL值占比99.5%</t>
+          <t>字段"name:el"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
@@ -10212,7 +10210,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>字段"name:el"NULL值占比100.0%</t>
+          <t>字段"happy_hours"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -10235,7 +10233,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>字段"happy_hours"NULL值占比100.0%</t>
+          <t>字段"contact:email"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
@@ -10258,7 +10256,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>字段"contact:email"NULL值占比100.0%</t>
+          <t>字段"addr:place"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -10281,7 +10279,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>字段"addr:place"NULL值占比99.9%</t>
+          <t>字段"was:name:en"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
@@ -10304,7 +10302,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>字段"was:name:en"NULL值占比99.9%</t>
+          <t>字段"was:description:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -10327,7 +10325,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>字段"was:description:en"NULL值占比100.0%</t>
+          <t>字段"internet_access:ssid"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -10350,7 +10348,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>字段"internet_access:ssid"NULL值占比100.0%</t>
+          <t>字段"diet:halal"NULL值占比99.7%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -10373,7 +10371,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>字段"diet:halal"NULL值占比99.7%</t>
+          <t>字段"was:cuisine"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
@@ -10396,7 +10394,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>字段"was:cuisine"NULL值占比99.9%</t>
+          <t>字段"charge"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
@@ -10419,7 +10417,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>字段"charge"NULL值占比99.9%</t>
+          <t>字段"contact:phone"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
@@ -10442,7 +10440,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>字段"contact:phone"NULL值占比99.8%</t>
+          <t>字段"name:zh_pinyin"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
@@ -10465,7 +10463,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>字段"name:zh_pinyin"NULL值占比99.9%</t>
+          <t>字段"not:brand:wikidata"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
@@ -10488,7 +10486,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>字段"not:brand:wikidata"NULL值占比99.9%</t>
+          <t>字段"description:no"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -10511,7 +10509,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>字段"description:no"NULL值占比100.0%</t>
+          <t>字段"name:it"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
@@ -10534,7 +10532,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>字段"name:it"NULL值占比100.0%</t>
+          <t>字段"food"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
@@ -10557,7 +10555,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>字段"food"NULL值占比99.9%</t>
+          <t>字段"addr:country"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
@@ -10580,7 +10578,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>字段"addr:country"NULL值占比100.0%</t>
+          <t>字段"brand:zn"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
@@ -10603,7 +10601,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>字段"brand:zn"NULL值占比99.8%</t>
+          <t>字段"diet:local"NULL值占比99.6%</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -10626,7 +10624,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>字段"diet:local"NULL值占比99.6%</t>
+          <t>字段"fixme"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -10649,7 +10647,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>字段"fixme"NULL值占比99.9%</t>
+          <t>字段"toilets"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
@@ -10672,7 +10670,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>字段"toilets"NULL值占比100.0%</t>
+          <t>字段"name:ja_rm"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
@@ -10695,7 +10693,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>字段"name:ja_rm"NULL值占比100.0%</t>
+          <t>字段"restaurant:theme"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
@@ -10718,7 +10716,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>字段"restaurant:theme"NULL值占比100.0%</t>
+          <t>字段"description:en"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
@@ -10741,7 +10739,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>字段"description:en"NULL值占比100.0%</t>
+          <t>字段"beauty"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
@@ -10764,7 +10762,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>字段"beauty"NULL值占比100.0%</t>
+          <t>字段"description:pt"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr"/>
@@ -10787,7 +10785,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>字段"description:pt"NULL值占比100.0%</t>
+          <t>字段"name:vi"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -10810,7 +10808,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>字段"name:vi"NULL值占比100.0%</t>
+          <t>字段"name:es"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -10833,7 +10831,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>字段"name:es"NULL值占比99.9%</t>
+          <t>字段"contact:instagram"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -10856,7 +10854,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>字段"contact:instagram"NULL值占比100.0%</t>
+          <t>字段"air_conditioning"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -10879,7 +10877,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>字段"air_conditioning"NULL值占比99.9%</t>
+          <t>字段"diet:healthy"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -10902,7 +10900,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>字段"diet:healthy"NULL值占比99.9%</t>
+          <t>字段"self_service"NULL值占比99.8%</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -10925,7 +10923,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>字段"self_service"NULL值占比99.8%</t>
+          <t>字段"diet:noodle"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -10948,7 +10946,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>字段"diet:noodle"NULL值占比100.0%</t>
+          <t>字段"ref"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -10971,7 +10969,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>字段"ref"NULL值占比100.0%</t>
+          <t>字段"breakfast"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -10994,7 +10992,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>字段"breakfast"NULL值占比100.0%</t>
+          <t>字段"brand:yue"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -11017,7 +11015,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>字段"brand:yue"NULL值占比100.0%</t>
+          <t>字段"name:yue"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -11040,7 +11038,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>字段"name:yue"NULL值占比100.0%</t>
+          <t>字段"addr:full"NULL值占比99.3%</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
@@ -11063,7 +11061,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>字段"addr:full"NULL值占比99.3%</t>
+          <t>字段"mobile"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
@@ -11086,7 +11084,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>字段"mobile"NULL值占比100.0%</t>
+          <t>字段"diet:chicken"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -11109,7 +11107,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>字段"diet:chicken"NULL值占比100.0%</t>
+          <t>字段"diet:fish"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -11132,7 +11130,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>字段"diet:fish"NULL值占比100.0%</t>
+          <t>字段"diet:meat"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
@@ -11155,7 +11153,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>字段"diet:meat"NULL值占比99.9%</t>
+          <t>字段"fast_food"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -11178,7 +11176,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>字段"fast_food"NULL值占比99.9%</t>
+          <t>字段"roof:levels"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -11201,7 +11199,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>字段"roof:levels"NULL值占比100.0%</t>
+          <t>字段"roof:shape"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -11224,7 +11222,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>字段"roof:shape"NULL值占比100.0%</t>
+          <t>字段"heritage:operator"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -11247,7 +11245,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>字段"heritage:operator"NULL值占比100.0%</t>
+          <t>字段"heritage:ref"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -11270,7 +11268,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>字段"heritage:ref"NULL值占比100.0%</t>
+          <t>字段"was:building"NULL值占比100.0%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -11283,20 +11281,24 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>NULL比例</t>
+          <t>域值范围</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>字段"was:building"NULL值占比100.0%</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr"/>
+          <t>字段"building"有2个非法值</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>['college', 'university']</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -11306,22 +11308,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>域值范围</t>
+          <t>面重叠检查</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>字段"building"有2个非法值</t>
+          <t>发现2对面重叠 (全量2537个要素过多，仅抽样前100个检查)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>['college', 'university']</t>
+          <t>[{'要素A': 42, '要素B': 44, '重叠面积': 1e-07}, {'要素A': 43, '要素B': 44, '重叠面积': 3e-08}]</t>
         </is>
       </c>
     </row>
@@ -11333,42 +11335,38 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>面重叠检查</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>发现2对面重叠 (全量2537个要素过多，仅抽样前100个检查)</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>[{'要素A': 42, '要素B': 44, '重叠面积': 1e-07}, {'要素A': 43, '要素B': 44, '重叠面积': 3e-08}]</t>
-        </is>
-      </c>
+          <t>业务逻辑</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>shanghai_poi.geojson</t>
+          <t>shanghai_roads.geojson</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>业务逻辑</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr"/>
+          <t>NULL比例</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>字段"ref"NULL值占比98.4%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr"/>
     </row>
     <row r="460">
@@ -11389,7 +11387,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>字段"junction"NULL值占比99.9%</t>
+          <t>字段"lanes"NULL值占比76.8%</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -11412,7 +11410,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>字段"tunnel"NULL值占比99.3%</t>
+          <t>字段"bridge"NULL值占比94.9%</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -11435,7 +11433,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>字段"access"NULL值占比98.8%</t>
+          <t>字段"maxspeed"NULL值占比96.7%</t>
         </is>
       </c>
       <c r="E462" t="inlineStr"/>
@@ -11458,7 +11456,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>字段"width"NULL值占比99.9%</t>
+          <t>字段"junction"NULL值占比99.9%</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -11471,17 +11469,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>线自相交检查</t>
+          <t>NULL比例</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>1条线自相交</t>
+          <t>字段"tunnel"NULL值占比99.3%</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -11494,17 +11492,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>长度一致性</t>
+          <t>NULL比例</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>11805条道路声明的长度与几何长度偏差&gt;5%</t>
+          <t>字段"access"NULL值占比98.8%</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -11517,20 +11515,89 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>NULL比例</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>字段"width"NULL值占比99.9%</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>shanghai_roads.geojson</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>线自相交检查</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1条线自相交</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>shanghai_roads.geojson</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>长度一致性</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>11805条道路声明的长度与几何长度偏差&gt;5%</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>shanghai_roads.geojson</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
+      <c r="C469" t="inlineStr">
         <is>
           <t>ID唯一性</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr">
+      <c r="D469" t="inlineStr">
         <is>
           <t>ID字段"osmid"有重复</t>
         </is>
       </c>
-      <c r="E466" t="inlineStr"/>
+      <c r="E469" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11547,27 +11614,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>记录数</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -11738,32 +11805,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>文件名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>要素数</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>几何类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>字段数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>经度范围</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>纬度范围</t>
         </is>
@@ -11816,12 +11883,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>121.277~121.600</t>
+          <t>121.089~121.600</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.002~31.300</t>
+          <t>31.013~31.319</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11911,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>121.404~121.564</t>
+          <t>121.408~121.550</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.172~31.293</t>
+          <t>31.172~31.321</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11991,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
